--- a/data/trans_dic/IP12B$otros-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor</t>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,19</t>
+          <t>0,0; 26,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,03</t>
+          <t>0,0; 46,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,79</t>
+          <t>0,0; 44,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,13</t>
+          <t>0,0; 22,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,63</t>
+          <t>0,0; 24,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 15,91</t>
+          <t>0,0; 16,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 24,89</t>
+          <t>5,7; 25,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,04; 32,75</t>
+          <t>8,98; 31,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 33,45</t>
+          <t>10,59; 33,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,13</t>
+          <t>2,59; 14,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 26,68</t>
+          <t>7,24; 27,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 21,79</t>
+          <t>7,75; 22,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 16,88</t>
+          <t>5,25; 16,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 25,66</t>
+          <t>10,63; 25,04</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 49,25</t>
+          <t>6,18; 49,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 37,76</t>
+          <t>4,37; 39,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,15</t>
+          <t>0,0; 24,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,72</t>
+          <t>0,0; 39,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,36</t>
+          <t>0,0; 36,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 33,9</t>
+          <t>6,38; 34,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 29,37</t>
+          <t>5,86; 31,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,4</t>
+          <t>0,0; 17,38</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,89</t>
+          <t>3,06; 17,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 22,26</t>
+          <t>7,37; 22,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,1</t>
+          <t>7,02; 23,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 27,83</t>
+          <t>10,1; 26,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,43</t>
+          <t>3,88; 15,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 20,65</t>
+          <t>5,61; 21,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,26</t>
+          <t>8,17; 19,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,03</t>
+          <t>7,11; 16,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 18,67</t>
+          <t>8,04; 18,16</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2712</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2577</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3120</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2549</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4211</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6065</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5430</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8198</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11495</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5028</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1998; 8858</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2857; 10135</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3320; 10396</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1173; 6654</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2635; 9930</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4726; 13660</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4214; 12950</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7247; 17072</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2945</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4325</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1336</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>531; 4278</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>707; 6444</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4116</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3889</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4095</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1178; 6395</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1606; 8611</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4513</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11878</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>13589</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>12830</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1344; 7551</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4517; 13485</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3871; 12972</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4716; 12604</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2467; 9817</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2686; 10056</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7404; 17859</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>8877; 20553</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8280; 18700</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$otros-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,96</t>
+          <t>0,0; 26,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,82</t>
+          <t>0,0; 48,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,27</t>
+          <t>0,0; 39,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,84</t>
+          <t>0,0; 27,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,61</t>
+          <t>0,0; 24,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,97</t>
+          <t>2,03; 17,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 25,27</t>
+          <t>5,57; 23,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 31,85</t>
+          <t>9,36; 31,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 33,16</t>
+          <t>9,48; 33,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 14,69</t>
+          <t>2,81; 16,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 27,3</t>
+          <t>7,21; 26,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 22,4</t>
+          <t>6,91; 21,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 16,12</t>
+          <t>5,55; 16,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 25,04</t>
+          <t>10,5; 26,13</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 49,77</t>
+          <t>6,14; 50,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 39,82</t>
+          <t>4,35; 38,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,61</t>
+          <t>0,0; 24,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,46</t>
+          <t>0,0; 39,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,5</t>
+          <t>0,0; 34,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 34,66</t>
+          <t>6,37; 32,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 31,43</t>
+          <t>7,04; 29,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,38</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 17,21</t>
+          <t>3,14; 17,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,0</t>
+          <t>6,94; 21,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 23,53</t>
+          <t>7,77; 22,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,98</t>
+          <t>9,46; 28,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,44</t>
+          <t>3,64; 15,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 21,01</t>
+          <t>5,23; 20,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 19,71</t>
+          <t>8,52; 19,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,46</t>
+          <t>7,0; 16,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,16</t>
+          <t>7,74; 18,01</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2712</t>
+          <t>0; 2668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2577</t>
+          <t>0; 2675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>0; 2751</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2549</t>
+          <t>0; 3104</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4211</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5028</t>
+          <t>603; 5220</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1998; 8858</t>
+          <t>1952; 8396</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2857; 10135</t>
+          <t>2978; 9930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3320; 10396</t>
+          <t>2971; 10425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1173; 6654</t>
+          <t>1273; 7571</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2635; 9930</t>
+          <t>2623; 9605</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4726; 13660</t>
+          <t>4212; 12852</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4214; 12950</t>
+          <t>4459; 13573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7247; 17072</t>
+          <t>7160; 17818</t>
         </is>
       </c>
     </row>
@@ -1632,27 +1632,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>531; 4278</t>
+          <t>528; 4310</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>707; 6444</t>
+          <t>704; 6157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4116</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3889</t>
+          <t>0; 3893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4095</t>
+          <t>0; 3816</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1178; 6395</t>
+          <t>1175; 5921</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1606; 8611</t>
+          <t>1930; 8106</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4513</t>
+          <t>0; 4100</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1344; 7551</t>
+          <t>1378; 7814</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4517; 13485</t>
+          <t>4255; 13414</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3871; 12972</t>
+          <t>4281; 12226</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4716; 12604</t>
+          <t>4420; 13198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2467; 9817</t>
+          <t>2311; 9887</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2686; 10056</t>
+          <t>2505; 9701</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7404; 17859</t>
+          <t>7715; 17813</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8877; 20553</t>
+          <t>8735; 20341</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8280; 18700</t>
+          <t>7974; 18549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$otros-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 47,03</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 43,79</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 26,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 48,6</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,03</t>
+          <t>0,0; 27,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,82</t>
+          <t>0,0; 24,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,7</t>
+          <t>0,0; 22,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,64%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>19,06%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,88%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 17,62</t>
+          <t>9,2; 33,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 23,95</t>
+          <t>2,82; 15,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 31,21</t>
+          <t>7,32; 26,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 33,26</t>
+          <t>2,0; 15,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 16,71</t>
+          <t>5,8; 24,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 26,41</t>
+          <t>10,04; 32,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 21,08</t>
+          <t>7,09; 21,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 16,89</t>
+          <t>5,4; 16,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 26,13</t>
+          <t>10,59; 25,66</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,94%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>21,01%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,2%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,99%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 50,13</t>
+          <t>0,0; 33,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 38,05</t>
+          <t>0,0; 39,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,5</t>
+          <t>6,03; 49,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,02</t>
+          <t>4,33; 37,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 26,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 32,09</t>
+          <t>6,26; 33,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 29,58</t>
+          <t>6,49; 29,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>0,0; 19,4</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>13,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,81</t>
+          <t>10,09; 27,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,89</t>
+          <t>4,05; 15,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 22,18</t>
+          <t>5,4; 20,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 28,26</t>
+          <t>4,07; 17,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,56</t>
+          <t>7,5; 22,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 20,27</t>
+          <t>7,56; 22,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 19,67</t>
+          <t>8,27; 19,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,29</t>
+          <t>6,88; 16,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 18,01</t>
+          <t>7,72; 18,67</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,22 +1200,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 2589</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3086</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2668</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2675</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2751</t>
+          <t>0; 2735</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3104</t>
+          <t>0; 2693</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4226</t>
+          <t>0; 3872</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6232</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5430</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1966</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4700</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6065</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6232</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5430</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>603; 5220</t>
+          <t>2884; 10485</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1952; 8396</t>
+          <t>1278; 6852</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2978; 9930</t>
+          <t>2661; 9703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2971; 10425</t>
+          <t>591; 4714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1273; 7571</t>
+          <t>2033; 8724</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2623; 9605</t>
+          <t>3196; 10421</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4212; 12852</t>
+          <t>4322; 13285</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4459; 13573</t>
+          <t>4339; 13566</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7160; 17818</t>
+          <t>7224; 17494</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1806</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2945</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1336</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>528; 4310</t>
+          <t>0; 3323</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704; 6157</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>518; 4234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3816</t>
+          <t>701; 6111</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4374</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1175; 5921</t>
+          <t>1155; 6256</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1930; 8106</t>
+          <t>1779; 8048</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4100</t>
+          <t>0; 5040</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8301</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7401</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8106</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5429</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1378; 7814</t>
+          <t>4714; 12997</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4255; 13414</t>
+          <t>2571; 9810</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4281; 12226</t>
+          <t>2585; 9882</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4420; 13198</t>
+          <t>1786; 7849</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2311; 9887</t>
+          <t>4596; 13643</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2505; 9701</t>
+          <t>4168; 12183</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7715; 17813</t>
+          <t>7496; 17444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8735; 20341</t>
+          <t>8587; 20013</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7974; 18549</t>
+          <t>7951; 19226</t>
         </is>
       </c>
     </row>
